--- a/data/trans_dic/P70B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,73; 86,43</t>
+          <t>76,93; 86,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,72; 88,38</t>
+          <t>80,14; 88,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,07; 86,19</t>
+          <t>79,64; 86,14</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,87; 95,38</t>
+          <t>81,68; 94,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,83; 88,12</t>
+          <t>81,9; 87,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,92; 93,08</t>
+          <t>83,03; 94,07</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,78; 90,43</t>
+          <t>80,45; 90,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,48; 90,75</t>
+          <t>82,24; 90,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,92; 89,39</t>
+          <t>82,91; 89,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,83; 90,99</t>
+          <t>84,85; 91,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,33; 92,24</t>
+          <t>83,27; 92,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,04; 90,74</t>
+          <t>85,19; 90,67</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>84,17; 90,95</t>
+          <t>84,0; 91,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,89; 88,28</t>
+          <t>83,94; 88,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,78; 89,35</t>
+          <t>84,67; 89,29</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que concilia su vida profesional y laboral</t>
+          <t>Población que concilia su vida profesional y laboral (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>256523; 288929</t>
+          <t>257173; 287976</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>206617; 226221</t>
+          <t>205110; 225475</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>472600; 508769</t>
+          <t>470060; 508480</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>659355; 768121</t>
+          <t>657779; 763533</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>328045; 353248</t>
+          <t>328325; 352546</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1000204; 1122820</t>
+          <t>1001507; 1134778</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>283964; 317899</t>
+          <t>282828; 316650</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>266841; 293596</t>
+          <t>266065; 293554</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>559748; 603421</t>
+          <t>559715; 604532</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>400588; 429654</t>
+          <t>400668; 429734</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>401302; 444209</t>
+          <t>401006; 444436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>811058; 865473</t>
+          <t>812546; 864794</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1652582; 1785734</t>
+          <t>1649331; 1795233</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1226398; 1290624</t>
+          <t>1227209; 1292206</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2904039; 3060596</t>
+          <t>2900291; 3058549</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P70B_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P70B_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,93; 86,14</t>
+          <t>78,76; 87,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,14; 88,09</t>
+          <t>80,52; 88,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,64; 86,14</t>
+          <t>80,65; 86,46</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>84,37%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,68; 94,81</t>
+          <t>79,62; 87,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,9; 87,94</t>
+          <t>81,96; 87,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,03; 94,07</t>
+          <t>81,79; 86,85</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80,45; 90,07</t>
+          <t>83,07; 90,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,24; 90,74</t>
+          <t>81,79; 88,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,91; 89,55</t>
+          <t>84,04; 89,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,85; 91,01</t>
+          <t>83,83; 90,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,27; 92,29</t>
+          <t>83,62; 89,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,19; 90,67</t>
+          <t>84,58; 88,87</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,52%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>84,0; 91,43</t>
+          <t>83,5; 87,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,94; 88,39</t>
+          <t>84,01; 87,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,67; 89,29</t>
+          <t>84,24; 86,71</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>274135</t>
+          <t>305996</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>216449</t>
+          <t>234332</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490584</t>
+          <t>540328</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>257173; 287976</t>
+          <t>289923; 321179</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>205110; 225475</t>
+          <t>222623; 243794</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>470060; 508480</t>
+          <t>519868; 557311</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>710538</t>
+          <t>526255</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>341062</t>
+          <t>381732</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1051600</t>
+          <t>907987</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>657779; 763533</t>
+          <t>499756; 547229</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>328325; 352546</t>
+          <t>367614; 394430</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1001507; 1134778</t>
+          <t>880214; 934700</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>303215</t>
+          <t>362530</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>279597</t>
+          <t>290081</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>582812</t>
+          <t>652611</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>282828; 316650</t>
+          <t>343853; 376233</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>266065; 293554</t>
+          <t>276976; 300987</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>559715; 604532</t>
+          <t>632482; 671978</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>416396</t>
+          <t>452577</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>420562</t>
+          <t>388992</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836957</t>
+          <t>841569</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>400668; 429734</t>
+          <t>434136; 468459</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>401006; 444436</t>
+          <t>376011; 401413</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>812546; 864794</t>
+          <t>818364; 859870</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1704284</t>
+          <t>1647358</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1257670</t>
+          <t>1295137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2961954</t>
+          <t>2942495</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1649331; 1795233</t>
+          <t>1609585; 1682397</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1227209; 1292206</t>
+          <t>1271312; 1320028</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2900291; 3058549</t>
+          <t>2898616; 2983553</t>
         </is>
       </c>
     </row>
